--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.86716</v>
+        <v>16.96877</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62728</v>
+        <v>16.24139</v>
       </c>
       <c r="E2" t="n">
-        <v>16.51912</v>
+        <v>16.35522</v>
       </c>
       <c r="F2" t="n">
-        <v>42.89732</v>
+        <v>42.6474</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05079</v>
+        <v>0.04935</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81281</v>
+        <v>1.83621</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88093</v>
+        <v>16.69704</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73421</v>
+        <v>16.4904</v>
       </c>
       <c r="E3" t="n">
-        <v>16.61036</v>
+        <v>16.6073</v>
       </c>
       <c r="F3" t="n">
-        <v>43.20097</v>
+        <v>42.16012</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05126</v>
+        <v>0.05029</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82755</v>
+        <v>1.82303</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.60623</v>
+        <v>16.90119</v>
       </c>
       <c r="D4" t="n">
-        <v>16.65948</v>
+        <v>16.72977</v>
       </c>
       <c r="E4" t="n">
-        <v>16.45113</v>
+        <v>16.86044</v>
       </c>
       <c r="F4" t="n">
-        <v>42.57492</v>
+        <v>43.19247</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05085</v>
+        <v>0.04949</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83474</v>
+        <v>1.84377</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.47055</v>
+        <v>16.74896</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8302</v>
+        <v>15.9459</v>
       </c>
       <c r="E6" t="n">
-        <v>16.24331</v>
+        <v>16.3889</v>
       </c>
       <c r="F6" t="n">
-        <v>21.90434</v>
+        <v>21.66571</v>
       </c>
       <c r="G6" t="n">
-        <v>34.14463</v>
+        <v>34.34837</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.92786</v>
+        <v>16.69166</v>
       </c>
       <c r="D7" t="n">
-        <v>15.89063</v>
+        <v>15.8045</v>
       </c>
       <c r="E7" t="n">
-        <v>16.47509</v>
+        <v>16.23441</v>
       </c>
       <c r="F7" t="n">
-        <v>21.43594</v>
+        <v>21.93386</v>
       </c>
       <c r="G7" t="n">
-        <v>34.50533</v>
+        <v>33.68635</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.68257</v>
+        <v>16.48509</v>
       </c>
       <c r="D8" t="n">
-        <v>15.66329</v>
+        <v>16.10844</v>
       </c>
       <c r="E8" t="n">
-        <v>16.47011</v>
+        <v>16.44091</v>
       </c>
       <c r="F8" t="n">
-        <v>21.81278</v>
+        <v>22.17651</v>
       </c>
       <c r="G8" t="n">
-        <v>33.48544</v>
+        <v>34.88079</v>
       </c>
     </row>
   </sheetData>
